--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/KENTUCKY_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/KENTUCKY_2017.xlsx
@@ -2659,7 +2659,7 @@
         <v>40</v>
       </c>
       <c r="D128">
-        <v>0.009267840593141797</v>
+        <v>0.009267840593141796</v>
       </c>
     </row>
     <row r="129">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C141">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C219">
@@ -5989,7 +5989,7 @@
         <v>40</v>
       </c>
       <c r="D313">
-        <v>0.009267840593141797</v>
+        <v>0.009267840593141796</v>
       </c>
     </row>
     <row r="314">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C528">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C548">
